--- a/etf_holdings/2026-09-27_errors.xlsx
+++ b/etf_holdings/2026-09-27_errors.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-27 22:06:28</t>
+          <t>2026-09-27 22:16:37</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -473,15 +473,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-27 22:07:28</t>
+          <t>2026-09-27 22:16:43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00991A/holdings", waiting until "networkidle"
-</t>
+          <t>00991A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
@@ -498,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-27 22:07:35</t>
+          <t>2026-09-27 22:16:50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +517,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-27 22:07:43</t>
+          <t>2026-09-27 22:16:57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -542,7 +539,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-27 22:07:51</t>
+          <t>2026-09-27 22:17:04</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -564,15 +561,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-27 22:08:51</t>
+          <t>2026-09-27 22:17:10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
-</t>
+          <t>00985A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
@@ -589,15 +583,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-27 22:09:51</t>
+          <t>2026-09-27 22:17:17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00992A/holdings", waiting until "networkidle"
-</t>
+          <t>00992A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
@@ -614,15 +605,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-27 22:10:51</t>
+          <t>2026-09-27 22:17:24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00990A/holdings", waiting until "networkidle"
-</t>
+          <t>00990A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
@@ -639,15 +627,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-27 22:11:51</t>
+          <t>2026-09-27 22:17:31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00405A/holdings", waiting until "networkidle"
-</t>
+          <t>00405A 未抓到任何持股資料</t>
         </is>
       </c>
     </row>
@@ -664,7 +649,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-27 22:11:58</t>
+          <t>2026-09-27 22:17:39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -686,7 +671,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-27 22:12:06</t>
+          <t>2026-09-27 22:17:45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -708,7 +693,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-27 22:12:13</t>
+          <t>2026-09-27 22:17:52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
